--- a/dataCleaned/incubation_chemistry_data.xlsx
+++ b/dataCleaned/incubation_chemistry_data.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Water_chemistry_data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sediment_Hg_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starting_PW_chemistry" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">incubationID</t>
   </si>
@@ -661,6 +662,12 @@
   </si>
   <si>
     <t xml:space="preserve">PCaMM_SCHM_196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">original_doc_mgC_L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">original_SUVA254</t>
   </si>
 </sst>
 </file>
@@ -799,6 +806,18 @@
     <tableColumn id="22" name="sed_percentMeHg_amb"/>
     <tableColumn id="23" name="sed_percentMeHg_201"/>
     <tableColumn id="24" name="sed_percentMeHg_204"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:C5" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C5"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="treatment"/>
+    <tableColumn id="2" name="original_doc_mgC_L"/>
+    <tableColumn id="3" name="original_SUVA254"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10088,4 +10107,73 @@
     <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="n">
+        <v>121.32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.195</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/dataCleaned/incubation_chemistry_data.xlsx
+++ b/dataCleaned/incubation_chemistry_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t xml:space="preserve">incubationID</t>
   </si>
@@ -148,6 +148,15 @@
     <t xml:space="preserve">sulfide_ppm_QA</t>
   </si>
   <si>
+    <t xml:space="preserve">PW_THg_amb_ppt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW_THg_201_ppt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW_THg_204_ppt</t>
+  </si>
+  <si>
     <t xml:space="preserve">PW_MeHg_amb_ppt</t>
   </si>
   <si>
@@ -155,6 +164,15 @@
   </si>
   <si>
     <t xml:space="preserve">PW_MeHg_204_ppt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW_percentMeHg_amb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW_percentMeHg_201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PW_percentMeHg_204</t>
   </si>
   <si>
     <t xml:space="preserve">PCaMM_inc_101</t>
@@ -723,9 +741,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:AU25" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:AU25"/>
-  <tableColumns count="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:BA25" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:BA25"/>
+  <tableColumns count="53">
     <tableColumn id="1" name="incubationID"/>
     <tableColumn id="2" name="experimentTypeID"/>
     <tableColumn id="3" name="treatment"/>
@@ -770,9 +788,15 @@
     <tableColumn id="42" name="DOC_AnalysisDate"/>
     <tableColumn id="43" name="sulfide_ppm"/>
     <tableColumn id="44" name="sulfide_ppm_QA"/>
-    <tableColumn id="45" name="PW_MeHg_amb_ppt"/>
-    <tableColumn id="46" name="PW_MeHg_201_ppt"/>
-    <tableColumn id="47" name="PW_MeHg_204_ppt"/>
+    <tableColumn id="45" name="PW_THg_amb_ppt"/>
+    <tableColumn id="46" name="PW_THg_201_ppt"/>
+    <tableColumn id="47" name="PW_THg_204_ppt"/>
+    <tableColumn id="48" name="PW_MeHg_amb_ppt"/>
+    <tableColumn id="49" name="PW_MeHg_201_ppt"/>
+    <tableColumn id="50" name="PW_MeHg_204_ppt"/>
+    <tableColumn id="51" name="PW_percentMeHg_amb"/>
+    <tableColumn id="52" name="PW_percentMeHg_201"/>
+    <tableColumn id="53" name="PW_percentMeHg_204"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1247,16 +1271,34 @@
       <c r="AU1" t="s">
         <v>46</v>
       </c>
+      <c r="AV1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>45483.6083333333</v>
@@ -1273,7 +1315,7 @@
         <v>1.40187204886115</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K2" t="n">
         <v>0.639303549</v>
@@ -1336,7 +1378,7 @@
       </c>
       <c r="AN2"/>
       <c r="AO2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP2" s="1" t="n">
         <v>45495</v>
@@ -1345,27 +1387,45 @@
         <v>0.0250206593381198</v>
       </c>
       <c r="AR2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS2" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0.970649288690827</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AW2" t="n">
         <v>0.236183026247461</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AX2" t="n">
         <v>0.254336071677509</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25.2773252263236</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>25.9541787085122</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>25.6905122906575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>45483.6152777778</v>
@@ -1413,16 +1473,22 @@
       <c r="AS3"/>
       <c r="AT3"/>
       <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>45483.6194444444</v>
@@ -1470,16 +1536,22 @@
       <c r="AS4"/>
       <c r="AT4"/>
       <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>45483.6256944444</v>
@@ -1488,112 +1560,112 @@
         <v>28.419775427936</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
         <v>0.195585169</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I5" t="n">
         <v>0.688200965894137</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
         <v>0.093376951</v>
       </c>
       <c r="L5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
         <v>6.291377104</v>
       </c>
       <c r="N5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O5" t="n">
         <v>-41.72546766</v>
       </c>
       <c r="P5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q5" t="n">
         <v>0.022341426</v>
       </c>
       <c r="R5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S5" t="n">
         <v>0.018754549</v>
       </c>
       <c r="T5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U5" t="n">
         <v>0.020858604</v>
       </c>
       <c r="V5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W5" t="n">
         <v>1.191253699</v>
       </c>
       <c r="X5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y5" t="n">
         <v>0.721422265827407</v>
       </c>
       <c r="Z5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA5" t="n">
         <v>5.0147395181844</v>
       </c>
       <c r="AB5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC5" t="n">
         <v>3.909325787537</v>
       </c>
       <c r="AD5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE5" t="n">
         <v>2.52638611105408</v>
       </c>
       <c r="AF5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG5" t="n">
         <v>1.26663252961112</v>
       </c>
       <c r="AH5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI5" t="n">
         <v>1.2181219679764</v>
       </c>
       <c r="AJ5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK5" t="n">
         <v>1.76927589887127</v>
       </c>
       <c r="AL5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM5" t="n">
         <v>0.459332198920686</v>
       </c>
       <c r="AN5" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO5" t="s">
         <v>57</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>51</v>
       </c>
       <c r="AP5" s="1" t="n">
         <v>45495</v>
@@ -1602,27 +1674,45 @@
         <v>0.0284170483855791</v>
       </c>
       <c r="AR5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1.36316549723797</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AW5" t="n">
         <v>0.708848415659534</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AX5" t="n">
         <v>0.403965550031752</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>36.8423107361613</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>47.5737191717808</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>43.9092989164947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>45483.63125</v>
@@ -1631,112 +1721,112 @@
         <v>64.3198894213089</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
         <v>0.735391607</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I6" t="n">
         <v>1.14333468794237</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K6" t="n">
         <v>0.389285947</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
         <v>5.686701227</v>
       </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O6" t="n">
         <v>-2400.871051</v>
       </c>
       <c r="P6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
         <v>0.015986316</v>
       </c>
       <c r="R6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S6" t="n">
         <v>0.019394326</v>
       </c>
       <c r="T6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U6" t="n">
         <v>0.018332817</v>
       </c>
       <c r="V6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W6" t="n">
         <v>0.824278002</v>
       </c>
       <c r="X6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y6" t="n">
         <v>0.803366663161393</v>
       </c>
       <c r="Z6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA6" t="n">
         <v>6.12985674097274</v>
       </c>
       <c r="AB6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC6" t="n">
         <v>4.08095255964338</v>
       </c>
       <c r="AD6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE6" t="n">
         <v>7.29686932073673</v>
       </c>
       <c r="AF6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG6" t="n">
         <v>5.65026756476203</v>
       </c>
       <c r="AH6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI6" t="n">
         <v>3.33770405858013</v>
       </c>
       <c r="AJ6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK6" t="n">
         <v>1.4177083853064</v>
       </c>
       <c r="AL6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM6" t="n">
         <v>0.692138702311523</v>
       </c>
       <c r="AN6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO6" t="s">
         <v>57</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>51</v>
       </c>
       <c r="AP6" s="1" t="n">
         <v>45495</v>
@@ -1745,27 +1835,45 @@
         <v>0.0355074387192975</v>
       </c>
       <c r="AR6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS6" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1.31710950956852</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AW6" t="n">
         <v>1.00724376500213</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AX6" t="n">
         <v>1.19864518627489</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>22.4379814236546</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>45.3713407658616</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>42.6564123229499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
         <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>45483.6395833333</v>
@@ -1813,16 +1921,22 @@
       <c r="AS7"/>
       <c r="AT7"/>
       <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45483.6451388889</v>
@@ -1839,7 +1953,7 @@
         <v>1.33452496544666</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K8" t="n">
         <v>0.665057193</v>
@@ -1902,7 +2016,7 @@
       </c>
       <c r="AN8"/>
       <c r="AO8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP8" s="1" t="n">
         <v>45495</v>
@@ -1912,24 +2026,42 @@
       </c>
       <c r="AR8"/>
       <c r="AS8" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="AV8" t="n">
         <v>2.24598445285214</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AW8" t="n">
         <v>0.457001181169075</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AX8" t="n">
         <v>0.445080106891287</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>28.3226286614393</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.64432094684019</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.88026432994832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45483.6534722222</v>
@@ -1938,112 +2070,112 @@
         <v>23.6632934477414</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
         <v>0.21489774</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I9" t="n">
         <v>0.908148058403557</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K9" t="n">
         <v>0.100105987</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
         <v>6.573066409</v>
       </c>
       <c r="N9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O9" t="n">
         <v>-103.2882457</v>
       </c>
       <c r="P9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q9" t="n">
         <v>0.019093688</v>
       </c>
       <c r="R9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S9" t="n">
         <v>0.015780034</v>
       </c>
       <c r="T9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U9" t="n">
         <v>0.018059335</v>
       </c>
       <c r="V9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W9" t="n">
         <v>1.20999028</v>
       </c>
       <c r="X9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y9" t="n">
         <v>0.701682095235698</v>
       </c>
       <c r="Z9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA9" t="n">
         <v>6.77114804287066</v>
       </c>
       <c r="AB9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC9" t="n">
         <v>4.5551553292479</v>
       </c>
       <c r="AD9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE9" t="n">
         <v>2.50874704465127</v>
       </c>
       <c r="AF9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG9" t="n">
         <v>3.44165471356132</v>
       </c>
       <c r="AH9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI9" t="n">
         <v>0.768158977568646</v>
       </c>
       <c r="AJ9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK9" t="n">
         <v>1.44570219114115</v>
       </c>
       <c r="AL9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM9" t="n">
         <v>0.357530851726351</v>
       </c>
       <c r="AN9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO9" t="s">
         <v>57</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>51</v>
       </c>
       <c r="AP9" s="1" t="n">
         <v>45495</v>
@@ -2052,27 +2184,45 @@
         <v>0.0443669654672678</v>
       </c>
       <c r="AR9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS9" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1.64737802194996</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AW9" t="n">
         <v>0.39127228026161</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AX9" t="n">
         <v>0.207018090617505</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>35.9689524443223</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>39.5224525516778</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>27.9754176510142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>45488.8513888889</v>
@@ -2089,7 +2239,7 @@
         <v>1.28139355844344</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
         <v>0.701280797</v>
@@ -2152,7 +2302,7 @@
       </c>
       <c r="AN10"/>
       <c r="AO10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP10" s="1" t="n">
         <v>45495</v>
@@ -2161,27 +2311,45 @@
         <v>0.0000384180850479797</v>
       </c>
       <c r="AR10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS10" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0.135695706755724</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AW10" t="n">
         <v>0.0497214790148916</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AX10" t="n">
         <v>0.0235770051029145</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-12.9234006434022</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>5.99053964034839</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.8027427585346</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>45488.8541666667</v>
@@ -2259,7 +2427,7 @@
       </c>
       <c r="AN11"/>
       <c r="AO11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP11" s="1" t="n">
         <v>45495</v>
@@ -2268,27 +2436,45 @@
         <v>0.000000757078694625884</v>
       </c>
       <c r="AR11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS11" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0.346326981461449</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AW11" t="n">
         <v>0.20987033318934</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AX11" t="n">
         <v>0.114985302301906</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4.56895753906924</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.951361437848324</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.938655528995152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>45488.8569444444</v>
@@ -2366,7 +2552,7 @@
       </c>
       <c r="AN12"/>
       <c r="AO12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP12" s="1" t="n">
         <v>45495</v>
@@ -2375,27 +2561,45 @@
         <v>0.000183857936067737</v>
       </c>
       <c r="AR12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS12" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>155.27</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0.0175000670539475</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AW12" t="n">
         <v>0.0675568244774977</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AX12" t="n">
         <v>0.0371569674766444</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.0376426479973058</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.0435092577300816</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.0441032254915661</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>45488.8604166667</v>
@@ -2412,7 +2616,7 @@
         <v>6.3029019496121</v>
       </c>
       <c r="J13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K13" t="n">
         <v>1.324691801</v>
@@ -2475,7 +2679,7 @@
       </c>
       <c r="AN13"/>
       <c r="AO13" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP13" s="1" t="n">
         <v>45495</v>
@@ -2484,27 +2688,45 @@
         <v>0.0000078258767398746</v>
       </c>
       <c r="AR13" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS13" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="AV13" t="n">
         <v>0.170972324552234</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AW13" t="n">
         <v>0.306398934852809</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AX13" t="n">
         <v>0.135667678203937</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.9124421090854</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.68814840139289</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.2970141319688</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>45488.8708333333</v>
@@ -2582,7 +2804,7 @@
       </c>
       <c r="AN14"/>
       <c r="AO14" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP14" s="1" t="n">
         <v>45495</v>
@@ -2591,27 +2813,45 @@
         <v>0.00000156400544437253</v>
       </c>
       <c r="AR14" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS14" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0.369055549033111</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AW14" t="n">
         <v>0.344433419766502</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AX14" t="n">
         <v>0.16794796420068</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.57853028579521</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.05019892718156</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.79623491123722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s">
         <v>70</v>
       </c>
-      <c r="B15" t="s">
-        <v>64</v>
-      </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>45488.875</v>
@@ -2628,7 +2868,7 @@
         <v>5.13223829471847</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K15" t="n">
         <v>1.408568604</v>
@@ -2691,7 +2931,7 @@
       </c>
       <c r="AN15"/>
       <c r="AO15" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP15" s="1" t="n">
         <v>45495</v>
@@ -2700,27 +2940,45 @@
         <v>0.000000393050097183804</v>
       </c>
       <c r="AR15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0.0606252028171151</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AW15" t="n">
         <v>0.0339777486688594</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AX15" t="n">
         <v>0.0152637807286183</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.84832935418034</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.807072414937278</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.441149732040991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>45488.88125</v>
@@ -2798,7 +3056,7 @@
       </c>
       <c r="AN16"/>
       <c r="AO16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP16" s="1" t="n">
         <v>45495</v>
@@ -2807,27 +3065,45 @@
         <v>0.000000455009178451791</v>
       </c>
       <c r="AR16" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS16" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AV16" t="n">
         <v>0.307399746794094</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AW16" t="n">
         <v>0.175449368377441</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AX16" t="n">
         <v>0.0810292830750297</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.63930338648151</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.34244817593379</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.79268325387234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
         <v>72</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>45488.8868055556</v>
@@ -2905,7 +3181,7 @@
       </c>
       <c r="AN17"/>
       <c r="AO17" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AP17" s="1" t="n">
         <v>45495</v>
@@ -2914,27 +3190,45 @@
         <v>0.00000223368983392043</v>
       </c>
       <c r="AR17" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AS17" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="AV17" t="n">
         <v>0.271807099206334</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AW17" t="n">
         <v>0.13896817968736</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AX17" t="n">
         <v>0.0641857702309693</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>2.86414224664208</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.65366029956425</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.508603567598806</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>45504.5625</v>
@@ -2943,112 +3237,112 @@
         <v>139.956847045758</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
         <v>0.708665958</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
         <v>0.50634604376898</v>
       </c>
       <c r="J18" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K18" t="n">
         <v>0.290927154</v>
       </c>
       <c r="L18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M18" t="n">
         <v>9.988542436</v>
       </c>
       <c r="N18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O18" t="n">
         <v>69.65895629</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q18" t="n">
         <v>0.023567386</v>
       </c>
       <c r="R18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S18" t="n">
         <v>0.022340847</v>
       </c>
       <c r="T18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U18" t="n">
         <v>0.021042064</v>
       </c>
       <c r="V18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W18" t="n">
         <v>1.054901204</v>
       </c>
       <c r="X18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y18" t="n">
         <v>0.779786979</v>
       </c>
       <c r="Z18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA18" t="n">
         <v>8.556091784</v>
       </c>
       <c r="AB18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC18" t="n">
         <v>8.021682168</v>
       </c>
       <c r="AD18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE18" t="n">
         <v>9.78547441</v>
       </c>
       <c r="AF18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG18" t="n">
         <v>7.626231435</v>
       </c>
       <c r="AH18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI18" t="n">
         <v>4.261850431</v>
       </c>
       <c r="AJ18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK18" t="n">
         <v>1.467150361</v>
       </c>
       <c r="AL18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM18" t="n">
         <v>0.684953174</v>
       </c>
       <c r="AN18" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO18" t="s">
         <v>57</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>51</v>
       </c>
       <c r="AP18" s="1" t="n">
         <v>45897</v>
@@ -3058,24 +3352,42 @@
       </c>
       <c r="AR18"/>
       <c r="AS18" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>21.52</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0.860597203773484</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AW18" t="n">
         <v>0.0842311167488812</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AX18" t="n">
         <v>0.0502240439015396</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.4124848853713</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.391408535078444</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.344236078831663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>45504.5666666667</v>
@@ -3084,112 +3396,112 @@
         <v>82.5286242727453</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G19" t="n">
         <v>0.242435563</v>
       </c>
       <c r="H19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0.293759365476377</v>
       </c>
       <c r="J19" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K19" t="n">
         <v>0.097998782</v>
       </c>
       <c r="L19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M19" t="n">
         <v>8.762099891</v>
       </c>
       <c r="N19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O19" t="n">
         <v>204.6129395</v>
       </c>
       <c r="P19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q19" t="n">
         <v>0.032633882</v>
       </c>
       <c r="R19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S19" t="n">
         <v>0.017914437</v>
       </c>
       <c r="T19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U19" t="n">
         <v>0.022407794</v>
       </c>
       <c r="V19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W19" t="n">
         <v>1.821652679</v>
       </c>
       <c r="X19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y19" t="n">
         <v>1.31207164</v>
       </c>
       <c r="Z19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA19" t="n">
         <v>10.01705978</v>
       </c>
       <c r="AB19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC19" t="n">
         <v>9.002094376</v>
       </c>
       <c r="AD19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE19" t="n">
         <v>4.583184738</v>
       </c>
       <c r="AF19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG19" t="n">
         <v>1.415454564</v>
       </c>
       <c r="AH19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI19" t="n">
         <v>0.707787514</v>
       </c>
       <c r="AJ19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK19" t="n">
         <v>1.263433821</v>
       </c>
       <c r="AL19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM19" t="n">
         <v>0.284703128</v>
       </c>
       <c r="AN19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO19" t="s">
         <v>57</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>51</v>
       </c>
       <c r="AP19" s="1" t="n">
         <v>45897</v>
@@ -3199,24 +3511,42 @@
       </c>
       <c r="AR19"/>
       <c r="AS19" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AV19" t="n">
         <v>1.05276723893223</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AW19" t="n">
         <v>0.0877891158351935</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AX19" t="n">
         <v>0.075937537863519</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>14.0556373689216</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.634314420774519</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.697314397277493</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>45504.5708333333</v>
@@ -3225,112 +3555,112 @@
         <v>123.757596329965</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
         <v>0.376913147</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I20" t="n">
         <v>0.304557585293647</v>
       </c>
       <c r="J20" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K20" t="n">
         <v>0.188547776</v>
       </c>
       <c r="L20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M20" t="n">
         <v>9.494027701</v>
       </c>
       <c r="N20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O20" t="n">
         <v>23.0830697</v>
       </c>
       <c r="P20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q20" t="n">
         <v>0.024310579</v>
       </c>
       <c r="R20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S20" t="n">
         <v>0.019272591</v>
       </c>
       <c r="T20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U20" t="n">
         <v>0.024372567</v>
       </c>
       <c r="V20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W20" t="n">
         <v>1.261406868</v>
       </c>
       <c r="X20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y20" t="n">
         <v>1.004541541</v>
       </c>
       <c r="Z20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA20" t="n">
         <v>11.71246506</v>
       </c>
       <c r="AB20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC20" t="n">
         <v>10.13273435</v>
       </c>
       <c r="AD20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE20" t="n">
         <v>5.115644134</v>
       </c>
       <c r="AF20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG20" t="n">
         <v>1.645807139</v>
       </c>
       <c r="AH20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI20" t="n">
         <v>1.219531021</v>
       </c>
       <c r="AJ20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK20" t="n">
         <v>1.371667235</v>
       </c>
       <c r="AL20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM20" t="n">
         <v>0.349075557</v>
       </c>
       <c r="AN20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO20" t="s">
         <v>57</v>
-      </c>
-      <c r="AO20" t="s">
-        <v>51</v>
       </c>
       <c r="AP20" s="1" t="n">
         <v>45897</v>
@@ -3340,24 +3670,42 @@
       </c>
       <c r="AR20"/>
       <c r="AS20" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0.535714770291246</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AW20" t="n">
         <v>0.0130391256339815</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AX20" t="n">
         <v>0.00661384072529816</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12.0385341638482</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.415258778152276</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0.18630537254361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>45504.575</v>
@@ -3405,24 +3753,42 @@
       </c>
       <c r="AR21"/>
       <c r="AS21" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0.489224142074983</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AW21" t="n">
         <v>0.068730042042193</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AX21" t="n">
         <v>0.0925539229237279</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5.71523530461429</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.70637247730928</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.754925961857487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>45504.5798611111</v>
@@ -3431,112 +3797,112 @@
         <v>106.566985218804</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
         <v>0.776874571</v>
       </c>
       <c r="H22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I22" t="n">
         <v>0.729001171802803</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K22" t="n">
         <v>0.339501434</v>
       </c>
       <c r="L22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M22" t="n">
         <v>8.887895942</v>
       </c>
       <c r="N22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O22" t="n">
         <v>19.03291783</v>
       </c>
       <c r="P22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q22" t="n">
         <v>0.02110964</v>
       </c>
       <c r="R22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S22" t="n">
         <v>0.022031095</v>
       </c>
       <c r="T22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U22" t="n">
         <v>0.019823171</v>
       </c>
       <c r="V22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W22" t="n">
         <v>0.958174764</v>
       </c>
       <c r="X22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y22" t="n">
         <v>0.733111521</v>
       </c>
       <c r="Z22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA22" t="n">
         <v>9.089842421</v>
       </c>
       <c r="AB22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC22" t="n">
         <v>8.003802509</v>
       </c>
       <c r="AD22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE22" t="n">
         <v>10.3397439</v>
       </c>
       <c r="AF22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG22" t="n">
         <v>7.92644075</v>
       </c>
       <c r="AH22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI22" t="n">
         <v>4.561084212</v>
       </c>
       <c r="AJ22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK22" t="n">
         <v>1.452237525</v>
       </c>
       <c r="AL22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM22" t="n">
         <v>0.692501464</v>
       </c>
       <c r="AN22" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO22" t="s">
         <v>57</v>
-      </c>
-      <c r="AO22" t="s">
-        <v>51</v>
       </c>
       <c r="AP22" s="1" t="n">
         <v>45897</v>
@@ -3546,24 +3912,42 @@
       </c>
       <c r="AR22"/>
       <c r="AS22" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="AV22" t="n">
         <v>0.481024676384484</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AW22" t="n">
         <v>0.109547636749401</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AX22" t="n">
         <v>0.0501159592979798</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>4.78631518790531</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.636165137917541</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.412137823174176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
         <v>80</v>
       </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>45504.5833333333</v>
@@ -3572,112 +3956,112 @@
         <v>61.1089119004949</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G23" t="n">
         <v>0.248214474</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I23" t="n">
         <v>0.406183756641214</v>
       </c>
       <c r="J23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K23" t="n">
         <v>0.107501503</v>
       </c>
       <c r="L23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
         <v>7.565558185</v>
       </c>
       <c r="N23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O23" t="n">
         <v>58.13888888</v>
       </c>
       <c r="P23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q23" t="n">
         <v>0.027562055</v>
       </c>
       <c r="R23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S23" t="n">
         <v>0.017631828</v>
       </c>
       <c r="T23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U23" t="n">
         <v>0.021601179</v>
       </c>
       <c r="V23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W23" t="n">
         <v>1.563199004</v>
       </c>
       <c r="X23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y23" t="n">
         <v>0.823797054</v>
       </c>
       <c r="Z23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA23" t="n">
         <v>7.942693899</v>
       </c>
       <c r="AB23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC23" t="n">
         <v>6.736503062</v>
       </c>
       <c r="AD23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE23" t="n">
         <v>3.463642074</v>
       </c>
       <c r="AF23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG23" t="n">
         <v>1.407128725</v>
       </c>
       <c r="AH23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI23" t="n">
         <v>1.136741646</v>
       </c>
       <c r="AJ23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK23" t="n">
         <v>1.400626825</v>
       </c>
       <c r="AL23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM23" t="n">
         <v>0.457837617</v>
       </c>
       <c r="AN23" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO23" t="s">
         <v>57</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>51</v>
       </c>
       <c r="AP23" s="1" t="n">
         <v>45897</v>
@@ -3687,24 +4071,42 @@
       </c>
       <c r="AR23"/>
       <c r="AS23" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.66145620625462</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AW23" t="n">
         <v>0.171597069148546</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AX23" t="n">
         <v>0.167516704283148</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>16.7485504662764</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.799986336356859</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.773035091292791</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>45504.5854166667</v>
@@ -3752,16 +4154,22 @@
       <c r="AS24"/>
       <c r="AT24"/>
       <c r="AU24"/>
+      <c r="AV24"/>
+      <c r="AW24"/>
+      <c r="AX24"/>
+      <c r="AY24"/>
+      <c r="AZ24"/>
+      <c r="BA24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
         <v>82</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>76</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>45504.5902777778</v>
@@ -3770,112 +4178,112 @@
         <v>88.1138573980482</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G25" t="n">
         <v>0.735824568</v>
       </c>
       <c r="H25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I25" t="n">
         <v>0.835083821919138</v>
       </c>
       <c r="J25" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K25" t="n">
         <v>0.319504766</v>
       </c>
       <c r="L25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M25" t="n">
         <v>9.138734622</v>
       </c>
       <c r="N25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O25" t="n">
         <v>11.72636017</v>
       </c>
       <c r="P25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q25" t="n">
         <v>0.021497487</v>
       </c>
       <c r="R25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="S25" t="n">
         <v>0.022178995</v>
       </c>
       <c r="T25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U25" t="n">
         <v>0.020778212</v>
       </c>
       <c r="V25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W25" t="n">
         <v>0.96927238</v>
       </c>
       <c r="X25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Y25" t="n">
         <v>0.759759206</v>
       </c>
       <c r="Z25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AA25" t="n">
         <v>8.312593551</v>
       </c>
       <c r="AB25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AC25" t="n">
         <v>8.453061881</v>
       </c>
       <c r="AD25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AE25" t="n">
         <v>9.741953015</v>
       </c>
       <c r="AF25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AG25" t="n">
         <v>7.538534579</v>
       </c>
       <c r="AH25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AI25" t="n">
         <v>4.223960963</v>
       </c>
       <c r="AJ25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AK25" t="n">
         <v>1.490053717</v>
       </c>
       <c r="AL25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="AM25" t="n">
         <v>0.685053639</v>
       </c>
       <c r="AN25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO25" t="s">
         <v>57</v>
-      </c>
-      <c r="AO25" t="s">
-        <v>51</v>
       </c>
       <c r="AP25" s="1" t="n">
         <v>45897</v>
@@ -3885,13 +4293,31 @@
       </c>
       <c r="AR25"/>
       <c r="AS25" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="AV25" t="n">
         <v>2.56873831328022</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AW25" t="n">
         <v>0.27275048784475</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AX25" t="n">
         <v>0.23555906159193</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>19.8358170909669</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.23696366369501</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01534078272384</v>
       </c>
     </row>
   </sheetData>
@@ -3910,7 +4336,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -3919,13 +4345,13 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -3934,75 +4360,75 @@
         <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="K1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="L1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="M1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="O1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="P1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="Q1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="R1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="S1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="T1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="U1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="V1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="W1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="X1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4014,19 +4440,19 @@
         <v>2.302</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L2" t="n">
         <v>0.179</v>
       </c>
       <c r="M2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N2" t="n">
         <v>0.195</v>
       </c>
       <c r="O2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P2" t="n">
         <v>83.0583119010699</v>
@@ -4052,25 +4478,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4114,25 +4540,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" t="s">
         <v>112</v>
       </c>
-      <c r="F4" t="s">
-        <v>106</v>
-      </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4144,19 +4570,19 @@
         <v>2.11</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
         <v>0.157</v>
       </c>
       <c r="M4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N4" t="n">
         <v>0.17</v>
       </c>
       <c r="O4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P4" t="n">
         <v>85.0152634133985</v>
@@ -4182,25 +4608,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4244,25 +4670,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4306,25 +4732,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" t="s">
         <v>115</v>
       </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" t="s">
-        <v>109</v>
-      </c>
       <c r="G7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4336,19 +4762,19 @@
         <v>8.944</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
         <v>0.272</v>
       </c>
       <c r="M7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N7" t="n">
         <v>0.127</v>
       </c>
       <c r="O7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P7" t="n">
         <v>78.9219287378505</v>
@@ -4374,25 +4800,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" t="s">
         <v>112</v>
       </c>
-      <c r="F8" t="s">
-        <v>106</v>
-      </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4404,19 +4830,19 @@
         <v>6.593</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
         <v>1.318</v>
       </c>
       <c r="M8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N8" t="n">
         <v>0.693</v>
       </c>
       <c r="O8" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P8" t="n">
         <v>121.857293917417</v>
@@ -4442,25 +4868,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
         <v>117</v>
       </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4472,19 +4898,19 @@
         <v>11.42</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
         <v>0.543</v>
       </c>
       <c r="M9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N9" t="n">
         <v>0.296</v>
       </c>
       <c r="O9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P9" t="n">
         <v>129.526641003523</v>
@@ -4510,25 +4936,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" t="s">
         <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>45483.6194444444</v>
@@ -4572,25 +4998,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" t="s">
-        <v>49</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>45483.6194444444</v>
@@ -4634,25 +5060,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" t="s">
         <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F12" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" t="s">
-        <v>49</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>45483.6194444444</v>
@@ -4696,25 +5122,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" t="s">
         <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" t="s">
-        <v>49</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>45483.6194444444</v>
@@ -4758,25 +5184,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>45483.6256944444</v>
@@ -4820,25 +5246,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>45483.6256944444</v>
@@ -4882,25 +5308,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" t="s">
         <v>112</v>
       </c>
-      <c r="F16" t="s">
-        <v>106</v>
-      </c>
       <c r="G16" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>45483.6256944444</v>
@@ -4944,25 +5370,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>45483.6256944444</v>
@@ -5006,25 +5432,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>45483.63125</v>
@@ -5036,19 +5462,19 @@
         <v>7.51800644707133</v>
       </c>
       <c r="K18" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L18" t="n">
         <v>1.07703216821524</v>
       </c>
       <c r="M18" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N18" t="n">
         <v>1.21425568260249</v>
       </c>
       <c r="O18" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P18" t="n">
         <v>102.66</v>
@@ -5074,25 +5500,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>45483.63125</v>
@@ -5136,25 +5562,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" t="s">
         <v>131</v>
       </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" t="s">
-        <v>125</v>
-      </c>
       <c r="E20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" t="s">
         <v>112</v>
       </c>
-      <c r="F20" t="s">
-        <v>106</v>
-      </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>45483.63125</v>
@@ -5166,19 +5592,19 @@
         <v>2.276</v>
       </c>
       <c r="K20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
         <v>0.155</v>
       </c>
       <c r="M20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N20" t="n">
         <v>0.16</v>
       </c>
       <c r="O20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P20" t="n">
         <v>72.49</v>
@@ -5204,25 +5630,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>45483.63125</v>
@@ -5266,25 +5692,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5328,25 +5754,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" t="s">
         <v>60</v>
-      </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5390,25 +5816,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" t="s">
-        <v>54</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5424,13 +5850,13 @@
         <v>0.0181458631284047</v>
       </c>
       <c r="M24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="N24" t="n">
         <v>0.0100709035319977</v>
       </c>
       <c r="O24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="P24" t="n">
         <v>81.1734682471509</v>
@@ -5444,7 +5870,7 @@
         <v>0.220237382240923</v>
       </c>
       <c r="U24" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="V24" t="n">
         <v>2.34882747979559</v>
@@ -5458,25 +5884,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" t="s">
         <v>60</v>
-      </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" t="s">
-        <v>109</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5492,13 +5918,13 @@
         <v>0.0104742684732905</v>
       </c>
       <c r="M25" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="N25" t="n">
         <v>0.00897458688747322</v>
       </c>
       <c r="O25" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="P25" t="n">
         <v>83.745926304189</v>
@@ -5508,13 +5934,13 @@
         <v>0.336892404624331</v>
       </c>
       <c r="S25" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="T25" t="n">
         <v>0.323229803009704</v>
       </c>
       <c r="U25" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="V25" t="n">
         <v>2.45853287798554</v>
@@ -5528,25 +5954,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>45483.6451388889</v>
@@ -5590,25 +6016,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F27" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>45483.6451388889</v>
@@ -5652,25 +6078,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" t="s">
         <v>112</v>
       </c>
-      <c r="F28" t="s">
-        <v>106</v>
-      </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>45483.6451388889</v>
@@ -5714,25 +6140,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F29" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>45483.6451388889</v>
@@ -5776,25 +6202,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>45483.6534722222</v>
@@ -5838,25 +6264,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F31" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>45483.6534722222</v>
@@ -5900,25 +6326,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" t="s">
         <v>112</v>
       </c>
-      <c r="F32" t="s">
-        <v>106</v>
-      </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>45483.6534722222</v>
@@ -5962,25 +6388,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>45483.6534722222</v>
@@ -6024,25 +6450,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6054,19 +6480,19 @@
         <v>0.981077823178148</v>
       </c>
       <c r="K34" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L34" t="n">
         <v>0.128782933724382</v>
       </c>
       <c r="M34" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N34" t="n">
         <v>0.0675508324807259</v>
       </c>
       <c r="O34" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P34" t="n">
         <v>66.4715798960531</v>
@@ -6092,25 +6518,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G35" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6154,25 +6580,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
+        <v>118</v>
+      </c>
+      <c r="F36" t="s">
         <v>112</v>
       </c>
-      <c r="F36" t="s">
-        <v>106</v>
-      </c>
       <c r="G36" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6200,13 +6626,13 @@
         <v>0.244075621332505</v>
       </c>
       <c r="S36" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="T36" t="n">
         <v>0.327734154409668</v>
       </c>
       <c r="U36" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="V36" t="n">
         <v>0.9938461354049</v>
@@ -6220,25 +6646,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F37" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G37" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6282,25 +6708,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E38" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6344,25 +6770,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" t="s">
         <v>155</v>
       </c>
-      <c r="B39" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" t="s">
-        <v>64</v>
-      </c>
-      <c r="D39" t="s">
-        <v>149</v>
-      </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6406,25 +6832,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" t="s">
         <v>112</v>
       </c>
-      <c r="F40" t="s">
-        <v>106</v>
-      </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6468,25 +6894,25 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C41" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D41" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F41" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6530,25 +6956,25 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E42" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G42" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>45488.8569444444</v>
@@ -6592,25 +7018,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B43" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E43" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F43" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G43" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>45488.8569444444</v>
@@ -6654,25 +7080,25 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" t="s">
         <v>112</v>
       </c>
-      <c r="F44" t="s">
-        <v>106</v>
-      </c>
       <c r="G44" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>45488.8569444444</v>
@@ -6716,25 +7142,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F45" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>45488.8569444444</v>
@@ -6778,25 +7204,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E46" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F46" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>45488.8604166667</v>
@@ -6840,25 +7266,25 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C47" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E47" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F47" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>45488.8604166667</v>
@@ -6902,25 +7328,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E48" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48" t="s">
         <v>112</v>
       </c>
-      <c r="F48" t="s">
-        <v>106</v>
-      </c>
       <c r="G48" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>45488.8604166667</v>
@@ -6964,25 +7390,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F49" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>45488.8604166667</v>
@@ -7026,25 +7452,25 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E50" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G50" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7088,25 +7514,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D51" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E51" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G51" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7150,25 +7576,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52" t="s">
         <v>112</v>
       </c>
-      <c r="F52" t="s">
-        <v>106</v>
-      </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7212,25 +7638,25 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D53" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E53" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F53" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G53" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7242,19 +7668,19 @@
         <v>1.26532781926493</v>
       </c>
       <c r="K53" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L53" t="n">
         <v>0.164932241355841</v>
       </c>
       <c r="M53" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N53" t="n">
         <v>0.081522578710733</v>
       </c>
       <c r="O53" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P53" t="n">
         <v>60.1077111215496</v>
@@ -7280,25 +7706,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" t="s">
         <v>70</v>
       </c>
-      <c r="C54" t="s">
-        <v>64</v>
-      </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>45488.875</v>
@@ -7342,25 +7768,25 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" t="s">
         <v>70</v>
       </c>
-      <c r="C55" t="s">
-        <v>64</v>
-      </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>45488.875</v>
@@ -7372,19 +7798,19 @@
         <v>0.375637573938087</v>
       </c>
       <c r="K55" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L55" t="n">
         <v>0.0484397479695387</v>
       </c>
       <c r="M55" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N55" t="n">
         <v>0.0240115135776845</v>
       </c>
       <c r="O55" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P55" t="n">
         <v>43.34</v>
@@ -7410,25 +7836,25 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" t="s">
         <v>70</v>
       </c>
-      <c r="C56" t="s">
-        <v>64</v>
-      </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E56" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" t="s">
         <v>112</v>
       </c>
-      <c r="F56" t="s">
-        <v>106</v>
-      </c>
       <c r="G56" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>45488.875</v>
@@ -7472,25 +7898,25 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
         <v>70</v>
       </c>
-      <c r="C57" t="s">
-        <v>64</v>
-      </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F57" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>45488.875</v>
@@ -7502,19 +7928,19 @@
         <v>0.355902497805086</v>
       </c>
       <c r="K57" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L57" t="n">
         <v>0.0102097913725734</v>
       </c>
       <c r="M57" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N57" t="n">
         <v>0.00610457708891082</v>
       </c>
       <c r="O57" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P57" t="n">
         <v>36.1396822505471</v>
@@ -7540,25 +7966,25 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G58" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>45488.88125</v>
@@ -7602,25 +8028,25 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F59" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>45488.88125</v>
@@ -7632,19 +8058,19 @@
         <v>0.566464205038363</v>
       </c>
       <c r="K59" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L59" t="n">
         <v>0.131717493174213</v>
       </c>
       <c r="M59" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N59" t="n">
         <v>0.0596429888419606</v>
       </c>
       <c r="O59" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P59" t="n">
         <v>53.52</v>
@@ -7670,25 +8096,25 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
         <v>112</v>
       </c>
-      <c r="F60" t="s">
-        <v>106</v>
-      </c>
       <c r="G60" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>45488.88125</v>
@@ -7700,19 +8126,19 @@
         <v>0.525366296463023</v>
       </c>
       <c r="K60" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L60" t="n">
         <v>0.0560031631712287</v>
       </c>
       <c r="M60" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N60" t="n">
         <v>0.0260157579178137</v>
       </c>
       <c r="O60" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="P60" t="n">
         <v>46.1588752007606</v>
@@ -7738,25 +8164,25 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F61" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>45488.88125</v>
@@ -7768,19 +8194,19 @@
         <v>0.53</v>
       </c>
       <c r="K61" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L61" t="n">
         <v>0.066</v>
       </c>
       <c r="M61" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N61" t="n">
         <v>0.031</v>
       </c>
       <c r="O61" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P61" t="n">
         <v>50.0282071836672</v>
@@ -7806,25 +8232,25 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" t="s">
+        <v>155</v>
+      </c>
+      <c r="E62" t="s">
+        <v>111</v>
+      </c>
+      <c r="F62" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" t="s">
         <v>72</v>
-      </c>
-      <c r="C62" t="s">
-        <v>64</v>
-      </c>
-      <c r="D62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E62" t="s">
-        <v>105</v>
-      </c>
-      <c r="F62" t="s">
-        <v>106</v>
-      </c>
-      <c r="G62" t="s">
-        <v>66</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>45488.8868055556</v>
@@ -7868,25 +8294,25 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B63" t="s">
+        <v>78</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" t="s">
+        <v>155</v>
+      </c>
+      <c r="E63" t="s">
+        <v>111</v>
+      </c>
+      <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>72</v>
-      </c>
-      <c r="C63" t="s">
-        <v>64</v>
-      </c>
-      <c r="D63" t="s">
-        <v>149</v>
-      </c>
-      <c r="E63" t="s">
-        <v>105</v>
-      </c>
-      <c r="F63" t="s">
-        <v>109</v>
-      </c>
-      <c r="G63" t="s">
-        <v>66</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>45488.8868055556</v>
@@ -7930,25 +8356,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" t="s">
+        <v>112</v>
+      </c>
+      <c r="G64" t="s">
         <v>72</v>
-      </c>
-      <c r="C64" t="s">
-        <v>64</v>
-      </c>
-      <c r="D64" t="s">
-        <v>152</v>
-      </c>
-      <c r="E64" t="s">
-        <v>112</v>
-      </c>
-      <c r="F64" t="s">
-        <v>106</v>
-      </c>
-      <c r="G64" t="s">
-        <v>66</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>45488.8868055556</v>
@@ -7964,7 +8390,7 @@
         <v>0.023</v>
       </c>
       <c r="M64" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="N64" t="n">
         <v>0.016</v>
@@ -7994,25 +8420,25 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C65" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" t="s">
+        <v>158</v>
+      </c>
+      <c r="E65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" t="s">
         <v>72</v>
-      </c>
-      <c r="C65" t="s">
-        <v>64</v>
-      </c>
-      <c r="D65" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" t="s">
-        <v>112</v>
-      </c>
-      <c r="F65" t="s">
-        <v>109</v>
-      </c>
-      <c r="G65" t="s">
-        <v>66</v>
       </c>
       <c r="H65" s="1" t="n">
         <v>45488.8868055556</v>
@@ -8028,7 +8454,7 @@
         <v>0.025</v>
       </c>
       <c r="M65" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="N65" t="n">
         <v>0.019</v>
@@ -8058,25 +8484,25 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E66" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F66" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G66" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>45504.5625</v>
@@ -8120,25 +8546,25 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D67" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E67" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F67" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H67" s="1" t="n">
         <v>45504.5625</v>
@@ -8182,25 +8608,25 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F68" t="s">
         <v>112</v>
       </c>
-      <c r="F68" t="s">
-        <v>106</v>
-      </c>
       <c r="G68" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H68" s="1" t="n">
         <v>45504.5625</v>
@@ -8244,25 +8670,25 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D69" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E69" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F69" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H69" s="1" t="n">
         <v>45504.5625</v>
@@ -8306,25 +8732,25 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F70" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G70" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H70" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8368,25 +8794,25 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F71" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H71" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8430,25 +8856,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E72" t="s">
+        <v>118</v>
+      </c>
+      <c r="F72" t="s">
         <v>112</v>
       </c>
-      <c r="F72" t="s">
-        <v>106</v>
-      </c>
       <c r="G72" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H72" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8492,25 +8918,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E73" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F73" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H73" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8554,25 +8980,25 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F74" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G74" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H74" s="1" t="n">
         <v>45504.5708333333</v>
@@ -8616,25 +9042,25 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E75" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F75" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>45504.5708333333</v>
@@ -8646,19 +9072,19 @@
         <v>3.365</v>
       </c>
       <c r="K75" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L75" t="n">
         <v>0.038</v>
       </c>
       <c r="M75" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="N75" t="n">
         <v>0.029</v>
       </c>
       <c r="O75" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P75" t="n">
         <v>126.61</v>
@@ -8684,25 +9110,25 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E76" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" t="s">
         <v>112</v>
       </c>
-      <c r="F76" t="s">
-        <v>106</v>
-      </c>
       <c r="G76" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H76" s="1" t="n">
         <v>45504.5708333333</v>
@@ -8746,25 +9172,25 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D77" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E77" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F77" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H77" s="1" t="n">
         <v>45504.5708333333</v>
@@ -8808,25 +9234,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E78" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F78" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G78" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H78" s="1" t="n">
         <v>45504.575</v>
@@ -8870,25 +9296,25 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D79" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F79" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H79" s="1" t="n">
         <v>45504.575</v>
@@ -8900,19 +9326,19 @@
         <v>0.524</v>
       </c>
       <c r="K79" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L79" t="n">
         <v>0.159</v>
       </c>
       <c r="M79" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N79" t="n">
         <v>0.139</v>
       </c>
       <c r="O79" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P79" t="n">
         <v>141.07</v>
@@ -8938,25 +9364,25 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D80" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E80" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" t="s">
         <v>112</v>
       </c>
-      <c r="F80" t="s">
-        <v>106</v>
-      </c>
       <c r="G80" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H80" s="1" t="n">
         <v>45504.575</v>
@@ -9000,25 +9426,25 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E81" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F81" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H81" s="1" t="n">
         <v>45504.575</v>
@@ -9062,25 +9488,25 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E82" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F82" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G82" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H82" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9124,25 +9550,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D83" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F83" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H83" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9154,19 +9580,19 @@
         <v>0.984</v>
       </c>
       <c r="K83" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
       <c r="M83" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N83" t="n">
         <v>0.131</v>
       </c>
       <c r="O83" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P83" t="n">
         <v>129.87</v>
@@ -9192,25 +9618,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D84" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E84" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" t="s">
         <v>112</v>
       </c>
-      <c r="F84" t="s">
-        <v>106</v>
-      </c>
       <c r="G84" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H84" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9222,19 +9648,19 @@
         <v>0.692</v>
       </c>
       <c r="K84" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L84" t="n">
         <v>0.129</v>
       </c>
       <c r="M84" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N84" t="n">
         <v>0.076</v>
       </c>
       <c r="O84" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P84" t="n">
         <v>149.705440045385</v>
@@ -9260,25 +9686,25 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D85" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F85" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H85" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9322,25 +9748,25 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
         <v>80</v>
       </c>
-      <c r="C86" t="s">
-        <v>74</v>
-      </c>
       <c r="D86" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E86" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F86" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G86" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H86" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9384,25 +9810,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B87" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" t="s">
         <v>80</v>
       </c>
-      <c r="C87" t="s">
-        <v>74</v>
-      </c>
       <c r="D87" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F87" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H87" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9414,19 +9840,19 @@
         <v>3.551</v>
       </c>
       <c r="K87" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L87" t="n">
         <v>0.789</v>
       </c>
       <c r="M87" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N87" t="n">
         <v>0.765</v>
       </c>
       <c r="O87" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="P87" t="n">
         <v>144.314366031419</v>
@@ -9452,25 +9878,25 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B88" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" t="s">
         <v>80</v>
       </c>
-      <c r="C88" t="s">
-        <v>74</v>
-      </c>
       <c r="D88" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E88" t="s">
+        <v>118</v>
+      </c>
+      <c r="F88" t="s">
         <v>112</v>
       </c>
-      <c r="F88" t="s">
-        <v>106</v>
-      </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H88" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9514,25 +9940,25 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" t="s">
         <v>80</v>
       </c>
-      <c r="C89" t="s">
-        <v>74</v>
-      </c>
       <c r="D89" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F89" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H89" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9576,25 +10002,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C90" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E90" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F90" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G90" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H90" s="1" t="n">
         <v>45504.5854166667</v>
@@ -9638,25 +10064,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B91" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C91" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D91" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E91" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F91" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H91" s="1" t="n">
         <v>45504.5854166667</v>
@@ -9700,25 +10126,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C92" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E92" t="s">
+        <v>118</v>
+      </c>
+      <c r="F92" t="s">
         <v>112</v>
       </c>
-      <c r="F92" t="s">
-        <v>106</v>
-      </c>
       <c r="G92" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H92" s="1" t="n">
         <v>45504.5854166667</v>
@@ -9730,19 +10156,19 @@
         <v>2.824</v>
       </c>
       <c r="K92" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L92" t="n">
         <v>0.696</v>
       </c>
       <c r="M92" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N92" t="n">
         <v>0.31</v>
       </c>
       <c r="O92" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P92" t="n">
         <v>146.982367157245</v>
@@ -9768,25 +10194,25 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E93" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F93" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H93" s="1" t="n">
         <v>45504.5854166667</v>
@@ -9798,19 +10224,19 @@
         <v>1.796</v>
       </c>
       <c r="K93" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L93" t="n">
         <v>0.332</v>
       </c>
       <c r="M93" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N93" t="n">
         <v>0.155</v>
       </c>
       <c r="O93" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P93" t="n">
         <v>118.01</v>
@@ -9836,25 +10262,25 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" t="s">
+        <v>80</v>
+      </c>
+      <c r="D94" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94" t="s">
+        <v>111</v>
+      </c>
+      <c r="F94" t="s">
+        <v>112</v>
+      </c>
+      <c r="G94" t="s">
         <v>82</v>
-      </c>
-      <c r="C94" t="s">
-        <v>74</v>
-      </c>
-      <c r="D94" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" t="s">
-        <v>105</v>
-      </c>
-      <c r="F94" t="s">
-        <v>106</v>
-      </c>
-      <c r="G94" t="s">
-        <v>76</v>
       </c>
       <c r="H94" s="1" t="n">
         <v>45504.5902777778</v>
@@ -9866,19 +10292,19 @@
         <v>7.315</v>
       </c>
       <c r="K94" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L94" t="n">
         <v>0.576</v>
       </c>
       <c r="M94" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N94" t="n">
         <v>0.535</v>
       </c>
       <c r="O94" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P94" t="n">
         <v>127.45</v>
@@ -9904,25 +10330,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C95" t="s">
+        <v>80</v>
+      </c>
+      <c r="D95" t="s">
+        <v>110</v>
+      </c>
+      <c r="E95" t="s">
+        <v>111</v>
+      </c>
+      <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" t="s">
         <v>82</v>
-      </c>
-      <c r="C95" t="s">
-        <v>74</v>
-      </c>
-      <c r="D95" t="s">
-        <v>104</v>
-      </c>
-      <c r="E95" t="s">
-        <v>105</v>
-      </c>
-      <c r="F95" t="s">
-        <v>109</v>
-      </c>
-      <c r="G95" t="s">
-        <v>76</v>
       </c>
       <c r="H95" s="1" t="n">
         <v>45504.5902777778</v>
@@ -9934,19 +10360,19 @@
         <v>6.641</v>
       </c>
       <c r="K95" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L95" t="n">
         <v>0.577</v>
       </c>
       <c r="M95" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N95" t="n">
         <v>0.526</v>
       </c>
       <c r="O95" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P95" t="n">
         <v>119.02</v>
@@ -9972,25 +10398,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B96" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" t="s">
+        <v>80</v>
+      </c>
+      <c r="D96" t="s">
+        <v>117</v>
+      </c>
+      <c r="E96" t="s">
+        <v>118</v>
+      </c>
+      <c r="F96" t="s">
+        <v>112</v>
+      </c>
+      <c r="G96" t="s">
         <v>82</v>
-      </c>
-      <c r="C96" t="s">
-        <v>74</v>
-      </c>
-      <c r="D96" t="s">
-        <v>111</v>
-      </c>
-      <c r="E96" t="s">
-        <v>112</v>
-      </c>
-      <c r="F96" t="s">
-        <v>106</v>
-      </c>
-      <c r="G96" t="s">
-        <v>76</v>
       </c>
       <c r="H96" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10034,25 +10460,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C97" t="s">
+        <v>80</v>
+      </c>
+      <c r="D97" t="s">
+        <v>117</v>
+      </c>
+      <c r="E97" t="s">
+        <v>118</v>
+      </c>
+      <c r="F97" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" t="s">
         <v>82</v>
-      </c>
-      <c r="C97" t="s">
-        <v>74</v>
-      </c>
-      <c r="D97" t="s">
-        <v>111</v>
-      </c>
-      <c r="E97" t="s">
-        <v>112</v>
-      </c>
-      <c r="F97" t="s">
-        <v>109</v>
-      </c>
-      <c r="G97" t="s">
-        <v>76</v>
       </c>
       <c r="H97" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10064,19 +10490,19 @@
         <v>2.45</v>
       </c>
       <c r="K97" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L97" t="n">
         <v>0.583</v>
       </c>
       <c r="M97" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N97" t="n">
         <v>0.519</v>
       </c>
       <c r="O97" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="P97" t="n">
         <v>145.99</v>
@@ -10119,15 +10545,15 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B2" t="n">
         <v>121.32</v>
@@ -10138,7 +10564,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B3" t="n">
         <v>19.47</v>
@@ -10149,7 +10575,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B4" t="n">
         <v>7.72</v>
@@ -10160,7 +10586,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B5" t="n">
         <v>3.525</v>

--- a/dataCleaned/incubation_chemistry_data.xlsx
+++ b/dataCleaned/incubation_chemistry_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">incubationID</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t xml:space="preserve">sulfide_ppm_QA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methane_µM</t>
   </si>
   <si>
     <t xml:space="preserve">PW_THg_amb_ppt</t>
@@ -741,9 +744,9 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:BA25" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:BA25"/>
-  <tableColumns count="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:BB25" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:BB25"/>
+  <tableColumns count="54">
     <tableColumn id="1" name="incubationID"/>
     <tableColumn id="2" name="experimentTypeID"/>
     <tableColumn id="3" name="treatment"/>
@@ -788,15 +791,16 @@
     <tableColumn id="42" name="DOC_AnalysisDate"/>
     <tableColumn id="43" name="sulfide_ppm"/>
     <tableColumn id="44" name="sulfide_ppm_QA"/>
-    <tableColumn id="45" name="PW_THg_amb_ppt"/>
-    <tableColumn id="46" name="PW_THg_201_ppt"/>
-    <tableColumn id="47" name="PW_THg_204_ppt"/>
-    <tableColumn id="48" name="PW_MeHg_amb_ppt"/>
-    <tableColumn id="49" name="PW_MeHg_201_ppt"/>
-    <tableColumn id="50" name="PW_MeHg_204_ppt"/>
-    <tableColumn id="51" name="PW_percentMeHg_amb"/>
-    <tableColumn id="52" name="PW_percentMeHg_201"/>
-    <tableColumn id="53" name="PW_percentMeHg_204"/>
+    <tableColumn id="45" name="methane_µM"/>
+    <tableColumn id="46" name="PW_THg_amb_ppt"/>
+    <tableColumn id="47" name="PW_THg_201_ppt"/>
+    <tableColumn id="48" name="PW_THg_204_ppt"/>
+    <tableColumn id="49" name="PW_MeHg_amb_ppt"/>
+    <tableColumn id="50" name="PW_MeHg_201_ppt"/>
+    <tableColumn id="51" name="PW_MeHg_204_ppt"/>
+    <tableColumn id="52" name="PW_percentMeHg_amb"/>
+    <tableColumn id="53" name="PW_percentMeHg_201"/>
+    <tableColumn id="54" name="PW_percentMeHg_204"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1289,16 +1293,19 @@
       <c r="BA1" t="s">
         <v>52</v>
       </c>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>45483.6083333333</v>
@@ -1315,7 +1322,7 @@
         <v>1.40187204886115</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K2" t="n">
         <v>0.639303549</v>
@@ -1378,7 +1385,7 @@
       </c>
       <c r="AN2"/>
       <c r="AO2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP2" s="1" t="n">
         <v>45495</v>
@@ -1387,45 +1394,48 @@
         <v>0.0250206593381198</v>
       </c>
       <c r="AR2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS2" t="n">
+        <v>9.64780556435041</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.84</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>0.91</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>0.99</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>0.970649288690827</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>0.236183026247461</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>0.254336071677509</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>25.2773252263236</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>25.9541787085122</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>25.6905122906575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>45483.6152777778</v>
@@ -1479,16 +1489,17 @@
       <c r="AY3"/>
       <c r="AZ3"/>
       <c r="BA3"/>
+      <c r="BB3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>45483.6194444444</v>
@@ -1542,16 +1553,17 @@
       <c r="AY4"/>
       <c r="AZ4"/>
       <c r="BA4"/>
+      <c r="BB4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>45483.6256944444</v>
@@ -1560,112 +1572,112 @@
         <v>28.419775427936</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
         <v>0.195585169</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I5" t="n">
         <v>0.688200965894137</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
         <v>0.093376951</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M5" t="n">
         <v>6.291377104</v>
       </c>
       <c r="N5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O5" t="n">
         <v>-41.72546766</v>
       </c>
       <c r="P5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q5" t="n">
         <v>0.022341426</v>
       </c>
       <c r="R5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S5" t="n">
         <v>0.018754549</v>
       </c>
       <c r="T5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U5" t="n">
         <v>0.020858604</v>
       </c>
       <c r="V5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W5" t="n">
         <v>1.191253699</v>
       </c>
       <c r="X5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y5" t="n">
         <v>0.721422265827407</v>
       </c>
       <c r="Z5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA5" t="n">
         <v>5.0147395181844</v>
       </c>
       <c r="AB5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC5" t="n">
         <v>3.909325787537</v>
       </c>
       <c r="AD5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE5" t="n">
         <v>2.52638611105408</v>
       </c>
       <c r="AF5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG5" t="n">
         <v>1.26663252961112</v>
       </c>
       <c r="AH5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI5" t="n">
         <v>1.2181219679764</v>
       </c>
       <c r="AJ5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK5" t="n">
         <v>1.76927589887127</v>
       </c>
       <c r="AL5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM5" t="n">
         <v>0.459332198920686</v>
       </c>
       <c r="AN5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP5" s="1" t="n">
         <v>45495</v>
@@ -1674,45 +1686,48 @@
         <v>0.0284170483855791</v>
       </c>
       <c r="AR5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS5" t="n">
+        <v>6.66807156378061</v>
+      </c>
+      <c r="AT5" t="n">
         <v>3.7</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>1.49</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.92</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>1.36316549723797</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>0.708848415659534</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>0.403965550031752</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>36.8423107361613</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>47.5737191717808</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>43.9092989164947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>45483.63125</v>
@@ -1721,112 +1736,112 @@
         <v>64.3198894213089</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
         <v>0.735391607</v>
       </c>
       <c r="H6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I6" t="n">
         <v>1.14333468794237</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K6" t="n">
         <v>0.389285947</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M6" t="n">
         <v>5.686701227</v>
       </c>
       <c r="N6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O6" t="n">
         <v>-2400.871051</v>
       </c>
       <c r="P6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q6" t="n">
         <v>0.015986316</v>
       </c>
       <c r="R6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S6" t="n">
         <v>0.019394326</v>
       </c>
       <c r="T6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U6" t="n">
         <v>0.018332817</v>
       </c>
       <c r="V6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W6" t="n">
         <v>0.824278002</v>
       </c>
       <c r="X6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y6" t="n">
         <v>0.803366663161393</v>
       </c>
       <c r="Z6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA6" t="n">
         <v>6.12985674097274</v>
       </c>
       <c r="AB6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC6" t="n">
         <v>4.08095255964338</v>
       </c>
       <c r="AD6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE6" t="n">
         <v>7.29686932073673</v>
       </c>
       <c r="AF6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG6" t="n">
         <v>5.65026756476203</v>
       </c>
       <c r="AH6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI6" t="n">
         <v>3.33770405858013</v>
       </c>
       <c r="AJ6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK6" t="n">
         <v>1.4177083853064</v>
       </c>
       <c r="AL6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM6" t="n">
         <v>0.692138702311523</v>
       </c>
       <c r="AN6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP6" s="1" t="n">
         <v>45495</v>
@@ -1835,45 +1850,48 @@
         <v>0.0355074387192975</v>
       </c>
       <c r="AR6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS6" t="n">
+        <v>10.6429348965085</v>
+      </c>
+      <c r="AT6" t="n">
         <v>5.87</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>2.22</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>2.81</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>1.31710950956852</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>1.00724376500213</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>1.19864518627489</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>22.4379814236546</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>45.3713407658616</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>42.6564123229499</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>45483.6395833333</v>
@@ -1927,16 +1945,17 @@
       <c r="AY7"/>
       <c r="AZ7"/>
       <c r="BA7"/>
+      <c r="BB7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45483.6451388889</v>
@@ -1953,7 +1972,7 @@
         <v>1.33452496544666</v>
       </c>
       <c r="J8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K8" t="n">
         <v>0.665057193</v>
@@ -2016,7 +2035,7 @@
       </c>
       <c r="AN8"/>
       <c r="AO8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP8" s="1" t="n">
         <v>45495</v>
@@ -2026,42 +2045,45 @@
       </c>
       <c r="AR8"/>
       <c r="AS8" t="n">
+        <v>2.5924947646112</v>
+      </c>
+      <c r="AT8" t="n">
         <v>7.93</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>9.84</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>9.12</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>2.24598445285214</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>0.457001181169075</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>0.445080106891287</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>28.3226286614393</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>4.64432094684019</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>4.88026432994832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45483.6534722222</v>
@@ -2070,112 +2092,112 @@
         <v>23.6632934477414</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
         <v>0.21489774</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I9" t="n">
         <v>0.908148058403557</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K9" t="n">
         <v>0.100105987</v>
       </c>
       <c r="L9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
         <v>6.573066409</v>
       </c>
       <c r="N9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O9" t="n">
         <v>-103.2882457</v>
       </c>
       <c r="P9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q9" t="n">
         <v>0.019093688</v>
       </c>
       <c r="R9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S9" t="n">
         <v>0.015780034</v>
       </c>
       <c r="T9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U9" t="n">
         <v>0.018059335</v>
       </c>
       <c r="V9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W9" t="n">
         <v>1.20999028</v>
       </c>
       <c r="X9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y9" t="n">
         <v>0.701682095235698</v>
       </c>
       <c r="Z9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA9" t="n">
         <v>6.77114804287066</v>
       </c>
       <c r="AB9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC9" t="n">
         <v>4.5551553292479</v>
       </c>
       <c r="AD9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE9" t="n">
         <v>2.50874704465127</v>
       </c>
       <c r="AF9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG9" t="n">
         <v>3.44165471356132</v>
       </c>
       <c r="AH9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI9" t="n">
         <v>0.768158977568646</v>
       </c>
       <c r="AJ9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK9" t="n">
         <v>1.44570219114115</v>
       </c>
       <c r="AL9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM9" t="n">
         <v>0.357530851726351</v>
       </c>
       <c r="AN9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP9" s="1" t="n">
         <v>45495</v>
@@ -2184,45 +2206,48 @@
         <v>0.0443669654672678</v>
       </c>
       <c r="AR9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS9" t="n">
+        <v>5.62240484378071</v>
+      </c>
+      <c r="AT9" t="n">
         <v>4.58</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>0.99</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>0.74</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>1.64737802194996</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>0.39127228026161</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>0.207018090617505</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>35.9689524443223</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>39.5224525516778</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>27.9754176510142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>45488.8513888889</v>
@@ -2239,7 +2264,7 @@
         <v>1.28139355844344</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
         <v>0.701280797</v>
@@ -2302,7 +2327,7 @@
       </c>
       <c r="AN10"/>
       <c r="AO10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP10" s="1" t="n">
         <v>45495</v>
@@ -2311,45 +2336,48 @@
         <v>0.0000384180850479797</v>
       </c>
       <c r="AR10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS10" t="n">
+        <v>55.580382451766</v>
+      </c>
+      <c r="AT10" t="n">
         <v>-1.05</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>0.83</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>0.62</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>0.135695706755724</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>0.0497214790148916</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>0.0235770051029145</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>-12.9234006434022</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>5.99053964034839</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>3.8027427585346</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" t="s">
         <v>71</v>
       </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>45488.8541666667</v>
@@ -2427,7 +2455,7 @@
       </c>
       <c r="AN11"/>
       <c r="AO11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP11" s="1" t="n">
         <v>45495</v>
@@ -2436,45 +2464,48 @@
         <v>0.000000757078694625884</v>
       </c>
       <c r="AR11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS11" t="n">
+        <v>113.352461442335</v>
+      </c>
+      <c r="AT11" t="n">
         <v>7.58</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>22.06</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>12.25</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>0.346326981461449</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.20987033318934</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>0.114985302301906</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>4.56895753906924</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>0.951361437848324</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>0.938655528995152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>45488.8569444444</v>
@@ -2552,7 +2583,7 @@
       </c>
       <c r="AN12"/>
       <c r="AO12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP12" s="1" t="n">
         <v>45495</v>
@@ -2561,45 +2592,48 @@
         <v>0.000183857936067737</v>
       </c>
       <c r="AR12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS12" t="n">
+        <v>94.7250358915922</v>
+      </c>
+      <c r="AT12" t="n">
         <v>46.49</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>155.27</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>84.25</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>0.0175000670539475</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>0.0675568244774977</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>0.0371569674766444</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>0.0376426479973058</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>0.0435092577300816</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>0.0441032254915661</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>45488.8604166667</v>
@@ -2616,7 +2650,7 @@
         <v>6.3029019496121</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
         <v>1.324691801</v>
@@ -2679,7 +2713,7 @@
       </c>
       <c r="AN13"/>
       <c r="AO13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP13" s="1" t="n">
         <v>45495</v>
@@ -2688,45 +2722,48 @@
         <v>0.0000078258767398746</v>
       </c>
       <c r="AR13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS13" t="n">
+        <v>197.478655164379</v>
+      </c>
+      <c r="AT13" t="n">
         <v>8.94</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>18.15</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>10.46</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>0.170972324552234</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>0.306398934852809</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>0.135667678203937</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>1.9124421090854</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>1.68814840139289</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>1.2970141319688</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>45488.8708333333</v>
@@ -2804,7 +2841,7 @@
       </c>
       <c r="AN14"/>
       <c r="AO14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP14" s="1" t="n">
         <v>45495</v>
@@ -2813,45 +2850,48 @@
         <v>0.00000156400544437253</v>
       </c>
       <c r="AR14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS14" t="n">
+        <v>285.880355871265</v>
+      </c>
+      <c r="AT14" t="n">
         <v>5.61</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>16.8</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>9.35</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>0.369055549033111</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>0.344433419766502</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>0.16794796420068</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
         <v>6.57853028579521</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BA14" t="n">
         <v>2.05019892718156</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BB14" t="n">
         <v>1.79623491123722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>45488.875</v>
@@ -2868,7 +2908,7 @@
         <v>5.13223829471847</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" t="n">
         <v>1.408568604</v>
@@ -2931,7 +2971,7 @@
       </c>
       <c r="AN15"/>
       <c r="AO15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP15" s="1" t="n">
         <v>45495</v>
@@ -2940,45 +2980,48 @@
         <v>0.000000393050097183804</v>
       </c>
       <c r="AR15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS15" t="n">
+        <v>139.335643210281</v>
+      </c>
+      <c r="AT15" t="n">
         <v>3.28</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>4.21</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>3.46</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.0606252028171151</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>0.0339777486688594</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>0.0152637807286183</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AZ15" t="n">
         <v>1.84832935418034</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BA15" t="n">
         <v>0.807072414937278</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>0.441149732040991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>45488.88125</v>
@@ -3056,7 +3099,7 @@
       </c>
       <c r="AN16"/>
       <c r="AO16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP16" s="1" t="n">
         <v>45495</v>
@@ -3065,45 +3108,48 @@
         <v>0.000000455009178451791</v>
       </c>
       <c r="AR16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS16" t="n">
+        <v>205.044374767887</v>
+      </c>
+      <c r="AT16" t="n">
         <v>4.63</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>7.49</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>4.52</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>0.307399746794094</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>0.175449368377441</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>0.0810292830750297</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
         <v>6.63930338648151</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BA16" t="n">
         <v>2.34244817593379</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>1.79268325387234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>45488.8868055556</v>
@@ -3181,7 +3227,7 @@
       </c>
       <c r="AN17"/>
       <c r="AO17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP17" s="1" t="n">
         <v>45495</v>
@@ -3190,45 +3236,48 @@
         <v>0.00000223368983392043</v>
       </c>
       <c r="AR17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS17" t="n">
+        <v>133.536768630724</v>
+      </c>
+      <c r="AT17" t="n">
         <v>9.49</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>21.26</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>12.62</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>0.271807099206334</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>0.13896817968736</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>0.0641857702309693</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AZ17" t="n">
         <v>2.86414224664208</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BA17" t="n">
         <v>0.65366029956425</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
         <v>0.508603567598806</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>45504.5625</v>
@@ -3237,112 +3286,112 @@
         <v>139.956847045758</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
         <v>0.708665958</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
         <v>0.50634604376898</v>
       </c>
       <c r="J18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" t="n">
         <v>0.290927154</v>
       </c>
       <c r="L18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M18" t="n">
         <v>9.988542436</v>
       </c>
       <c r="N18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O18" t="n">
         <v>69.65895629</v>
       </c>
       <c r="P18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q18" t="n">
         <v>0.023567386</v>
       </c>
       <c r="R18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S18" t="n">
         <v>0.022340847</v>
       </c>
       <c r="T18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U18" t="n">
         <v>0.021042064</v>
       </c>
       <c r="V18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W18" t="n">
         <v>1.054901204</v>
       </c>
       <c r="X18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y18" t="n">
         <v>0.779786979</v>
       </c>
       <c r="Z18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA18" t="n">
         <v>8.556091784</v>
       </c>
       <c r="AB18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC18" t="n">
         <v>8.021682168</v>
       </c>
       <c r="AD18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE18" t="n">
         <v>9.78547441</v>
       </c>
       <c r="AF18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG18" t="n">
         <v>7.626231435</v>
       </c>
       <c r="AH18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI18" t="n">
         <v>4.261850431</v>
       </c>
       <c r="AJ18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK18" t="n">
         <v>1.467150361</v>
       </c>
       <c r="AL18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM18" t="n">
         <v>0.684953174</v>
       </c>
       <c r="AN18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP18" s="1" t="n">
         <v>45897</v>
@@ -3352,42 +3401,45 @@
       </c>
       <c r="AR18"/>
       <c r="AS18" t="n">
+        <v>177.251844980536</v>
+      </c>
+      <c r="AT18" t="n">
         <v>10.23</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>21.52</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>14.59</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>0.860597203773484</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.0842311167488812</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>0.0502240439015396</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>8.4124848853713</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BA18" t="n">
         <v>0.391408535078444</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BB18" t="n">
         <v>0.344236078831663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>45504.5666666667</v>
@@ -3396,112 +3448,112 @@
         <v>82.5286242727453</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" t="n">
         <v>0.242435563</v>
       </c>
       <c r="H19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I19" t="n">
         <v>0.293759365476377</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K19" t="n">
         <v>0.097998782</v>
       </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M19" t="n">
         <v>8.762099891</v>
       </c>
       <c r="N19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O19" t="n">
         <v>204.6129395</v>
       </c>
       <c r="P19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q19" t="n">
         <v>0.032633882</v>
       </c>
       <c r="R19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S19" t="n">
         <v>0.017914437</v>
       </c>
       <c r="T19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U19" t="n">
         <v>0.022407794</v>
       </c>
       <c r="V19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W19" t="n">
         <v>1.821652679</v>
       </c>
       <c r="X19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y19" t="n">
         <v>1.31207164</v>
       </c>
       <c r="Z19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA19" t="n">
         <v>10.01705978</v>
       </c>
       <c r="AB19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC19" t="n">
         <v>9.002094376</v>
       </c>
       <c r="AD19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE19" t="n">
         <v>4.583184738</v>
       </c>
       <c r="AF19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG19" t="n">
         <v>1.415454564</v>
       </c>
       <c r="AH19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI19" t="n">
         <v>0.707787514</v>
       </c>
       <c r="AJ19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK19" t="n">
         <v>1.263433821</v>
       </c>
       <c r="AL19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM19" t="n">
         <v>0.284703128</v>
       </c>
       <c r="AN19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP19" s="1" t="n">
         <v>45897</v>
@@ -3511,42 +3563,45 @@
       </c>
       <c r="AR19"/>
       <c r="AS19" t="n">
+        <v>171.787955501704</v>
+      </c>
+      <c r="AT19" t="n">
         <v>7.49</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>13.84</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>10.89</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>1.05276723893223</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>0.0877891158351935</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>0.075937537863519</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
         <v>14.0556373689216</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BA19" t="n">
         <v>0.634314420774519</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
         <v>0.697314397277493</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>45504.5708333333</v>
@@ -3555,112 +3610,112 @@
         <v>123.757596329965</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G20" t="n">
         <v>0.376913147</v>
       </c>
       <c r="H20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I20" t="n">
         <v>0.304557585293647</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K20" t="n">
         <v>0.188547776</v>
       </c>
       <c r="L20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M20" t="n">
         <v>9.494027701</v>
       </c>
       <c r="N20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O20" t="n">
         <v>23.0830697</v>
       </c>
       <c r="P20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q20" t="n">
         <v>0.024310579</v>
       </c>
       <c r="R20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S20" t="n">
         <v>0.019272591</v>
       </c>
       <c r="T20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U20" t="n">
         <v>0.024372567</v>
       </c>
       <c r="V20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W20" t="n">
         <v>1.261406868</v>
       </c>
       <c r="X20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y20" t="n">
         <v>1.004541541</v>
       </c>
       <c r="Z20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA20" t="n">
         <v>11.71246506</v>
       </c>
       <c r="AB20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC20" t="n">
         <v>10.13273435</v>
       </c>
       <c r="AD20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE20" t="n">
         <v>5.115644134</v>
       </c>
       <c r="AF20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG20" t="n">
         <v>1.645807139</v>
       </c>
       <c r="AH20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI20" t="n">
         <v>1.219531021</v>
       </c>
       <c r="AJ20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK20" t="n">
         <v>1.371667235</v>
       </c>
       <c r="AL20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM20" t="n">
         <v>0.349075557</v>
       </c>
       <c r="AN20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP20" s="1" t="n">
         <v>45897</v>
@@ -3670,42 +3725,45 @@
       </c>
       <c r="AR20"/>
       <c r="AS20" t="n">
+        <v>357.350886242943</v>
+      </c>
+      <c r="AT20" t="n">
         <v>4.45</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>3.14</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>3.55</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>0.535714770291246</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>0.0130391256339815</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
         <v>0.00661384072529816</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AZ20" t="n">
         <v>12.0385341638482</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BA20" t="n">
         <v>0.415258778152276</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BB20" t="n">
         <v>0.18630537254361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>45504.575</v>
@@ -3753,42 +3811,45 @@
       </c>
       <c r="AR21"/>
       <c r="AS21" t="n">
+        <v>285.376413429949</v>
+      </c>
+      <c r="AT21" t="n">
         <v>8.56</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>9.73</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>12.26</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>0.489224142074983</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>0.068730042042193</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
         <v>0.0925539229237279</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
         <v>5.71523530461429</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BA21" t="n">
         <v>0.70637247730928</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
         <v>0.754925961857487</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>45504.5798611111</v>
@@ -3797,112 +3858,112 @@
         <v>106.566985218804</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
         <v>0.776874571</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I22" t="n">
         <v>0.729001171802803</v>
       </c>
       <c r="J22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K22" t="n">
         <v>0.339501434</v>
       </c>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M22" t="n">
         <v>8.887895942</v>
       </c>
       <c r="N22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O22" t="n">
         <v>19.03291783</v>
       </c>
       <c r="P22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q22" t="n">
         <v>0.02110964</v>
       </c>
       <c r="R22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S22" t="n">
         <v>0.022031095</v>
       </c>
       <c r="T22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U22" t="n">
         <v>0.019823171</v>
       </c>
       <c r="V22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W22" t="n">
         <v>0.958174764</v>
       </c>
       <c r="X22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y22" t="n">
         <v>0.733111521</v>
       </c>
       <c r="Z22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA22" t="n">
         <v>9.089842421</v>
       </c>
       <c r="AB22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC22" t="n">
         <v>8.003802509</v>
       </c>
       <c r="AD22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE22" t="n">
         <v>10.3397439</v>
       </c>
       <c r="AF22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG22" t="n">
         <v>7.92644075</v>
       </c>
       <c r="AH22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI22" t="n">
         <v>4.561084212</v>
       </c>
       <c r="AJ22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK22" t="n">
         <v>1.452237525</v>
       </c>
       <c r="AL22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM22" t="n">
         <v>0.692501464</v>
       </c>
       <c r="AN22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP22" s="1" t="n">
         <v>45897</v>
@@ -3912,42 +3973,45 @@
       </c>
       <c r="AR22"/>
       <c r="AS22" t="n">
+        <v>394.993628390858</v>
+      </c>
+      <c r="AT22" t="n">
         <v>10.05</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>17.22</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>12.16</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>0.481024676384484</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>0.109547636749401</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
         <v>0.0501159592979798</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
         <v>4.78631518790531</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BA22" t="n">
         <v>0.636165137917541</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
         <v>0.412137823174176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>45504.5833333333</v>
@@ -3956,112 +4020,112 @@
         <v>61.1089119004949</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G23" t="n">
         <v>0.248214474</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I23" t="n">
         <v>0.406183756641214</v>
       </c>
       <c r="J23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K23" t="n">
         <v>0.107501503</v>
       </c>
       <c r="L23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M23" t="n">
         <v>7.565558185</v>
       </c>
       <c r="N23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O23" t="n">
         <v>58.13888888</v>
       </c>
       <c r="P23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q23" t="n">
         <v>0.027562055</v>
       </c>
       <c r="R23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S23" t="n">
         <v>0.017631828</v>
       </c>
       <c r="T23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U23" t="n">
         <v>0.021601179</v>
       </c>
       <c r="V23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W23" t="n">
         <v>1.563199004</v>
       </c>
       <c r="X23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y23" t="n">
         <v>0.823797054</v>
       </c>
       <c r="Z23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA23" t="n">
         <v>7.942693899</v>
       </c>
       <c r="AB23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC23" t="n">
         <v>6.736503062</v>
       </c>
       <c r="AD23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE23" t="n">
         <v>3.463642074</v>
       </c>
       <c r="AF23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG23" t="n">
         <v>1.407128725</v>
       </c>
       <c r="AH23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI23" t="n">
         <v>1.136741646</v>
       </c>
       <c r="AJ23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK23" t="n">
         <v>1.400626825</v>
       </c>
       <c r="AL23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM23" t="n">
         <v>0.457837617</v>
       </c>
       <c r="AN23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP23" s="1" t="n">
         <v>45897</v>
@@ -4071,42 +4135,45 @@
       </c>
       <c r="AR23"/>
       <c r="AS23" t="n">
+        <v>303.57800148858</v>
+      </c>
+      <c r="AT23" t="n">
         <v>9.92</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>21.45</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>21.67</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>1.66145620625462</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>0.171597069148546</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
         <v>0.167516704283148</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
         <v>16.7485504662764</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BA23" t="n">
         <v>0.799986336356859</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>0.773035091292791</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>45504.5854166667</v>
@@ -4160,16 +4227,17 @@
       <c r="AY24"/>
       <c r="AZ24"/>
       <c r="BA24"/>
+      <c r="BB24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>45504.5902777778</v>
@@ -4178,112 +4246,112 @@
         <v>88.1138573980482</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" t="n">
         <v>0.735824568</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I25" t="n">
         <v>0.835083821919138</v>
       </c>
       <c r="J25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
         <v>0.319504766</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M25" t="n">
         <v>9.138734622</v>
       </c>
       <c r="N25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O25" t="n">
         <v>11.72636017</v>
       </c>
       <c r="P25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q25" t="n">
         <v>0.021497487</v>
       </c>
       <c r="R25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S25" t="n">
         <v>0.022178995</v>
       </c>
       <c r="T25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U25" t="n">
         <v>0.020778212</v>
       </c>
       <c r="V25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W25" t="n">
         <v>0.96927238</v>
       </c>
       <c r="X25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y25" t="n">
         <v>0.759759206</v>
       </c>
       <c r="Z25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AA25" t="n">
         <v>8.312593551</v>
       </c>
       <c r="AB25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC25" t="n">
         <v>8.453061881</v>
       </c>
       <c r="AD25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE25" t="n">
         <v>9.741953015</v>
       </c>
       <c r="AF25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG25" t="n">
         <v>7.538534579</v>
       </c>
       <c r="AH25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI25" t="n">
         <v>4.223960963</v>
       </c>
       <c r="AJ25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AK25" t="n">
         <v>1.490053717</v>
       </c>
       <c r="AL25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AM25" t="n">
         <v>0.685053639</v>
       </c>
       <c r="AN25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AO25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AP25" s="1" t="n">
         <v>45897</v>
@@ -4293,30 +4361,33 @@
       </c>
       <c r="AR25"/>
       <c r="AS25" t="n">
+        <v>262.497542662458</v>
+      </c>
+      <c r="AT25" t="n">
         <v>12.95</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>22.05</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>23.2</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>2.56873831328022</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>0.27275048784475</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
         <v>0.23555906159193</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AZ25" t="n">
         <v>19.8358170909669</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BA25" t="n">
         <v>1.23696366369501</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
         <v>1.01534078272384</v>
       </c>
     </row>
@@ -4336,7 +4407,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -4345,13 +4416,13 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -4360,75 +4431,75 @@
         <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4440,19 +4511,19 @@
         <v>2.302</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L2" t="n">
         <v>0.179</v>
       </c>
       <c r="M2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N2" t="n">
         <v>0.195</v>
       </c>
       <c r="O2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P2" t="n">
         <v>83.0583119010699</v>
@@ -4478,25 +4549,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4540,25 +4611,25 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4570,19 +4641,19 @@
         <v>2.11</v>
       </c>
       <c r="K4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L4" t="n">
         <v>0.157</v>
       </c>
       <c r="M4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N4" t="n">
         <v>0.17</v>
       </c>
       <c r="O4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P4" t="n">
         <v>85.0152634133985</v>
@@ -4608,25 +4679,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
         <v>119</v>
       </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>45483.6083333333</v>
@@ -4670,25 +4741,25 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4732,25 +4803,25 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4762,19 +4833,19 @@
         <v>8.944</v>
       </c>
       <c r="K7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L7" t="n">
         <v>0.272</v>
       </c>
       <c r="M7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N7" t="n">
         <v>0.127</v>
       </c>
       <c r="O7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P7" t="n">
         <v>78.9219287378505</v>
@@ -4800,25 +4871,25 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4830,19 +4901,19 @@
         <v>6.593</v>
       </c>
       <c r="K8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L8" t="n">
         <v>1.318</v>
       </c>
       <c r="M8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" t="n">
         <v>0.693</v>
       </c>
       <c r="O8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P8" t="n">
         <v>121.857293917417</v>
@@ -4868,25 +4939,25 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>45483.6152777778</v>
@@ -4898,19 +4969,19 @@
         <v>11.42</v>
       </c>
       <c r="K9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" t="n">
         <v>0.543</v>
       </c>
       <c r="M9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N9" t="n">
         <v>0.296</v>
       </c>
       <c r="O9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P9" t="n">
         <v>129.526641003523</v>
@@ -4936,25 +5007,25 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>45483.6194444444</v>
@@ -4998,25 +5069,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>45483.6194444444</v>
@@ -5060,25 +5131,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>45483.6194444444</v>
@@ -5122,25 +5193,25 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>45483.6194444444</v>
@@ -5184,25 +5255,25 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H14" s="1" t="n">
         <v>45483.6256944444</v>
@@ -5246,25 +5317,25 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H15" s="1" t="n">
         <v>45483.6256944444</v>
@@ -5308,25 +5379,25 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>45483.6256944444</v>
@@ -5370,25 +5441,25 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" t="s">
         <v>132</v>
       </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>131</v>
-      </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>45483.6256944444</v>
@@ -5432,25 +5503,25 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>45483.63125</v>
@@ -5462,19 +5533,19 @@
         <v>7.51800644707133</v>
       </c>
       <c r="K18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" t="n">
         <v>1.07703216821524</v>
       </c>
       <c r="M18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" t="n">
         <v>1.21425568260249</v>
       </c>
       <c r="O18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P18" t="n">
         <v>102.66</v>
@@ -5500,25 +5571,25 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" s="1" t="n">
         <v>45483.63125</v>
@@ -5562,25 +5633,25 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>45483.63125</v>
@@ -5592,19 +5663,19 @@
         <v>2.276</v>
       </c>
       <c r="K20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
         <v>0.155</v>
       </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N20" t="n">
         <v>0.16</v>
       </c>
       <c r="O20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P20" t="n">
         <v>72.49</v>
@@ -5630,25 +5701,25 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21" s="1" t="n">
         <v>45483.63125</v>
@@ -5692,25 +5763,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5754,25 +5825,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5816,25 +5887,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5850,13 +5921,13 @@
         <v>0.0181458631284047</v>
       </c>
       <c r="M24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N24" t="n">
         <v>0.0100709035319977</v>
       </c>
       <c r="O24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P24" t="n">
         <v>81.1734682471509</v>
@@ -5870,7 +5941,7 @@
         <v>0.220237382240923</v>
       </c>
       <c r="U24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V24" t="n">
         <v>2.34882747979559</v>
@@ -5884,25 +5955,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>45483.6395833333</v>
@@ -5918,13 +5989,13 @@
         <v>0.0104742684732905</v>
       </c>
       <c r="M25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N25" t="n">
         <v>0.00897458688747322</v>
       </c>
       <c r="O25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P25" t="n">
         <v>83.745926304189</v>
@@ -5934,13 +6005,13 @@
         <v>0.336892404624331</v>
       </c>
       <c r="S25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T25" t="n">
         <v>0.323229803009704</v>
       </c>
       <c r="U25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V25" t="n">
         <v>2.45853287798554</v>
@@ -5954,25 +6025,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>45483.6451388889</v>
@@ -6016,25 +6087,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>45483.6451388889</v>
@@ -6078,25 +6149,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>45483.6451388889</v>
@@ -6140,25 +6211,25 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>45483.6451388889</v>
@@ -6202,25 +6273,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>45483.6534722222</v>
@@ -6264,25 +6335,25 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>45483.6534722222</v>
@@ -6326,25 +6397,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>45483.6534722222</v>
@@ -6388,25 +6459,25 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H33" s="1" t="n">
         <v>45483.6534722222</v>
@@ -6450,25 +6521,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6480,19 +6551,19 @@
         <v>0.981077823178148</v>
       </c>
       <c r="K34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L34" t="n">
         <v>0.128782933724382</v>
       </c>
       <c r="M34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N34" t="n">
         <v>0.0675508324807259</v>
       </c>
       <c r="O34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P34" t="n">
         <v>66.4715798960531</v>
@@ -6518,25 +6589,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" t="s">
         <v>156</v>
       </c>
-      <c r="B35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" t="s">
-        <v>155</v>
-      </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6580,25 +6651,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6626,13 +6697,13 @@
         <v>0.244075621332505</v>
       </c>
       <c r="S36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T36" t="n">
         <v>0.327734154409668</v>
       </c>
       <c r="U36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="V36" t="n">
         <v>0.9938461354049</v>
@@ -6646,25 +6717,25 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" t="s">
         <v>159</v>
       </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" t="s">
-        <v>158</v>
-      </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37" s="1" t="n">
         <v>45488.8513888889</v>
@@ -6708,25 +6779,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
         <v>71</v>
       </c>
-      <c r="C38" t="s">
-        <v>70</v>
-      </c>
       <c r="D38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6770,25 +6841,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
         <v>71</v>
       </c>
-      <c r="C39" t="s">
-        <v>70</v>
-      </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F39" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H39" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6832,25 +6903,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
         <v>71</v>
       </c>
-      <c r="C40" t="s">
-        <v>70</v>
-      </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H40" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6894,25 +6965,25 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
         <v>71</v>
       </c>
-      <c r="C41" t="s">
-        <v>70</v>
-      </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>45488.8541666667</v>
@@ -6956,25 +7027,25 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H42" s="1" t="n">
         <v>45488.8569444444</v>
@@ -7018,25 +7089,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G43" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H43" s="1" t="n">
         <v>45488.8569444444</v>
@@ -7080,25 +7151,25 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F44" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H44" s="1" t="n">
         <v>45488.8569444444</v>
@@ -7142,25 +7213,25 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H45" s="1" t="n">
         <v>45488.8569444444</v>
@@ -7204,25 +7275,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>45488.8604166667</v>
@@ -7266,25 +7337,25 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H47" s="1" t="n">
         <v>45488.8604166667</v>
@@ -7328,25 +7399,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F48" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>45488.8604166667</v>
@@ -7390,25 +7461,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H49" s="1" t="n">
         <v>45488.8604166667</v>
@@ -7452,25 +7523,25 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7514,25 +7585,25 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F51" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7576,25 +7647,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H52" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7638,25 +7709,25 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>45488.8708333333</v>
@@ -7668,19 +7739,19 @@
         <v>1.26532781926493</v>
       </c>
       <c r="K53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L53" t="n">
         <v>0.164932241355841</v>
       </c>
       <c r="M53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N53" t="n">
         <v>0.081522578710733</v>
       </c>
       <c r="O53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" t="n">
         <v>60.1077111215496</v>
@@ -7706,25 +7777,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F54" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>45488.875</v>
@@ -7768,25 +7839,25 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E55" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H55" s="1" t="n">
         <v>45488.875</v>
@@ -7798,19 +7869,19 @@
         <v>0.375637573938087</v>
       </c>
       <c r="K55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L55" t="n">
         <v>0.0484397479695387</v>
       </c>
       <c r="M55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N55" t="n">
         <v>0.0240115135776845</v>
       </c>
       <c r="O55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P55" t="n">
         <v>43.34</v>
@@ -7836,25 +7907,25 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H56" s="1" t="n">
         <v>45488.875</v>
@@ -7898,25 +7969,25 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H57" s="1" t="n">
         <v>45488.875</v>
@@ -7928,19 +7999,19 @@
         <v>0.355902497805086</v>
       </c>
       <c r="K57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L57" t="n">
         <v>0.0102097913725734</v>
       </c>
       <c r="M57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N57" t="n">
         <v>0.00610457708891082</v>
       </c>
       <c r="O57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P57" t="n">
         <v>36.1396822505471</v>
@@ -7966,25 +8037,25 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H58" s="1" t="n">
         <v>45488.88125</v>
@@ -8028,25 +8099,25 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H59" s="1" t="n">
         <v>45488.88125</v>
@@ -8058,19 +8129,19 @@
         <v>0.566464205038363</v>
       </c>
       <c r="K59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L59" t="n">
         <v>0.131717493174213</v>
       </c>
       <c r="M59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N59" t="n">
         <v>0.0596429888419606</v>
       </c>
       <c r="O59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P59" t="n">
         <v>53.52</v>
@@ -8096,25 +8167,25 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H60" s="1" t="n">
         <v>45488.88125</v>
@@ -8126,19 +8197,19 @@
         <v>0.525366296463023</v>
       </c>
       <c r="K60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L60" t="n">
         <v>0.0560031631712287</v>
       </c>
       <c r="M60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N60" t="n">
         <v>0.0260157579178137</v>
       </c>
       <c r="O60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P60" t="n">
         <v>46.1588752007606</v>
@@ -8164,25 +8235,25 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G61" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H61" s="1" t="n">
         <v>45488.88125</v>
@@ -8194,19 +8265,19 @@
         <v>0.53</v>
       </c>
       <c r="K61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L61" t="n">
         <v>0.066</v>
       </c>
       <c r="M61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N61" t="n">
         <v>0.031</v>
       </c>
       <c r="O61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P61" t="n">
         <v>50.0282071836672</v>
@@ -8232,25 +8303,25 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H62" s="1" t="n">
         <v>45488.8868055556</v>
@@ -8294,25 +8365,25 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H63" s="1" t="n">
         <v>45488.8868055556</v>
@@ -8356,25 +8427,25 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H64" s="1" t="n">
         <v>45488.8868055556</v>
@@ -8390,7 +8461,7 @@
         <v>0.023</v>
       </c>
       <c r="M64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N64" t="n">
         <v>0.016</v>
@@ -8420,25 +8491,25 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H65" s="1" t="n">
         <v>45488.8868055556</v>
@@ -8454,7 +8525,7 @@
         <v>0.025</v>
       </c>
       <c r="M65" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N65" t="n">
         <v>0.019</v>
@@ -8484,25 +8555,25 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F66" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G66" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H66" s="1" t="n">
         <v>45504.5625</v>
@@ -8546,25 +8617,25 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G67" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H67" s="1" t="n">
         <v>45504.5625</v>
@@ -8608,25 +8679,25 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E68" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G68" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H68" s="1" t="n">
         <v>45504.5625</v>
@@ -8670,25 +8741,25 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E69" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H69" s="1" t="n">
         <v>45504.5625</v>
@@ -8732,25 +8803,25 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" t="s">
         <v>81</v>
       </c>
-      <c r="C70" t="s">
-        <v>80</v>
-      </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F70" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G70" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H70" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8794,25 +8865,25 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B71" t="s">
+        <v>82</v>
+      </c>
+      <c r="C71" t="s">
         <v>81</v>
       </c>
-      <c r="C71" t="s">
-        <v>80</v>
-      </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G71" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H71" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8856,25 +8927,25 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" t="s">
         <v>81</v>
       </c>
-      <c r="C72" t="s">
-        <v>80</v>
-      </c>
       <c r="D72" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E72" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F72" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G72" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H72" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8918,25 +8989,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B73" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73" t="s">
         <v>81</v>
       </c>
-      <c r="C73" t="s">
-        <v>80</v>
-      </c>
       <c r="D73" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E73" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G73" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H73" s="1" t="n">
         <v>45504.5666666667</v>
@@ -8980,25 +9051,25 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E74" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H74" s="1" t="n">
         <v>45504.5708333333</v>
@@ -9042,25 +9113,25 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E75" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G75" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H75" s="1" t="n">
         <v>45504.5708333333</v>
@@ -9072,19 +9143,19 @@
         <v>3.365</v>
       </c>
       <c r="K75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L75" t="n">
         <v>0.038</v>
       </c>
       <c r="M75" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N75" t="n">
         <v>0.029</v>
       </c>
       <c r="O75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P75" t="n">
         <v>126.61</v>
@@ -9110,25 +9181,25 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G76" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H76" s="1" t="n">
         <v>45504.5708333333</v>
@@ -9172,25 +9243,25 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D77" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E77" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H77" s="1" t="n">
         <v>45504.5708333333</v>
@@ -9234,25 +9305,25 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D78" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E78" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G78" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H78" s="1" t="n">
         <v>45504.575</v>
@@ -9296,25 +9367,25 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E79" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H79" s="1" t="n">
         <v>45504.575</v>
@@ -9326,19 +9397,19 @@
         <v>0.524</v>
       </c>
       <c r="K79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L79" t="n">
         <v>0.159</v>
       </c>
       <c r="M79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N79" t="n">
         <v>0.139</v>
       </c>
       <c r="O79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P79" t="n">
         <v>141.07</v>
@@ -9364,25 +9435,25 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E80" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F80" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H80" s="1" t="n">
         <v>45504.575</v>
@@ -9426,25 +9497,25 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D81" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E81" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H81" s="1" t="n">
         <v>45504.575</v>
@@ -9488,25 +9559,25 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E82" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F82" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G82" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H82" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9550,25 +9621,25 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E83" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G83" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H83" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9580,19 +9651,19 @@
         <v>0.984</v>
       </c>
       <c r="K83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
       <c r="M83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N83" t="n">
         <v>0.131</v>
       </c>
       <c r="O83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P83" t="n">
         <v>129.87</v>
@@ -9618,25 +9689,25 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E84" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G84" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H84" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9648,19 +9719,19 @@
         <v>0.692</v>
       </c>
       <c r="K84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L84" t="n">
         <v>0.129</v>
       </c>
       <c r="M84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N84" t="n">
         <v>0.076</v>
       </c>
       <c r="O84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P84" t="n">
         <v>149.705440045385</v>
@@ -9686,25 +9757,25 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D85" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H85" s="1" t="n">
         <v>45504.5798611111</v>
@@ -9748,25 +9819,25 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E86" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F86" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G86" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H86" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9810,25 +9881,25 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E87" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G87" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H87" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9840,19 +9911,19 @@
         <v>3.551</v>
       </c>
       <c r="K87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L87" t="n">
         <v>0.789</v>
       </c>
       <c r="M87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N87" t="n">
         <v>0.765</v>
       </c>
       <c r="O87" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P87" t="n">
         <v>144.314366031419</v>
@@ -9878,25 +9949,25 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D88" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G88" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H88" s="1" t="n">
         <v>45504.5833333333</v>
@@ -9940,25 +10011,25 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D89" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G89" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H89" s="1" t="n">
         <v>45504.5833333333</v>
@@ -10002,25 +10073,25 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D90" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E90" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F90" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G90" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H90" s="1" t="n">
         <v>45504.5854166667</v>
@@ -10064,25 +10135,25 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E91" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G91" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H91" s="1" t="n">
         <v>45504.5854166667</v>
@@ -10126,25 +10197,25 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E92" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G92" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H92" s="1" t="n">
         <v>45504.5854166667</v>
@@ -10156,19 +10227,19 @@
         <v>2.824</v>
       </c>
       <c r="K92" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L92" t="n">
         <v>0.696</v>
       </c>
       <c r="M92" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N92" t="n">
         <v>0.31</v>
       </c>
       <c r="O92" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P92" t="n">
         <v>146.982367157245</v>
@@ -10194,25 +10265,25 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B93" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E93" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G93" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H93" s="1" t="n">
         <v>45504.5854166667</v>
@@ -10224,19 +10295,19 @@
         <v>1.796</v>
       </c>
       <c r="K93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L93" t="n">
         <v>0.332</v>
       </c>
       <c r="M93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N93" t="n">
         <v>0.155</v>
       </c>
       <c r="O93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P93" t="n">
         <v>118.01</v>
@@ -10262,25 +10333,25 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E94" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G94" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H94" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10292,19 +10363,19 @@
         <v>7.315</v>
       </c>
       <c r="K94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L94" t="n">
         <v>0.576</v>
       </c>
       <c r="M94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N94" t="n">
         <v>0.535</v>
       </c>
       <c r="O94" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P94" t="n">
         <v>127.45</v>
@@ -10330,25 +10401,25 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B95" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E95" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G95" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H95" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10360,19 +10431,19 @@
         <v>6.641</v>
       </c>
       <c r="K95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L95" t="n">
         <v>0.577</v>
       </c>
       <c r="M95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N95" t="n">
         <v>0.526</v>
       </c>
       <c r="O95" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P95" t="n">
         <v>119.02</v>
@@ -10398,25 +10469,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B96" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D96" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E96" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F96" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G96" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H96" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10460,25 +10531,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B97" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D97" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E97" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F97" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G97" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H97" s="1" t="n">
         <v>45504.5902777778</v>
@@ -10490,19 +10561,19 @@
         <v>2.45</v>
       </c>
       <c r="K97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L97" t="n">
         <v>0.583</v>
       </c>
       <c r="M97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N97" t="n">
         <v>0.519</v>
       </c>
       <c r="O97" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P97" t="n">
         <v>145.99</v>
@@ -10545,15 +10616,15 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="n">
         <v>121.32</v>
@@ -10564,7 +10635,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" t="n">
         <v>19.47</v>
@@ -10575,7 +10646,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" t="n">
         <v>7.72</v>
@@ -10586,7 +10657,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="n">
         <v>3.525</v>
